--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487484_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487484_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>15.0486</v>
+        <v>14.1351</v>
       </c>
       <c r="E2" t="n">
-        <v>12.1627</v>
+        <v>11.4364</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8859</v>
+        <v>2.6987</v>
       </c>
       <c r="G2" t="n">
         <v>10.7903</v>
@@ -610,13 +610,13 @@
         <v>2.546</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7502</v>
+        <v>0.8368</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9679</v>
+        <v>1.2415</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2177</v>
+        <v>-0.4048</v>
       </c>
       <c r="V2" t="n">
         <v>0.9412</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6256</v>
+        <v>4.4198</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8782</v>
+        <v>4.4854</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2527</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>4.2721</v>
@@ -688,13 +688,13 @@
         <v>1.3709</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2371</v>
+        <v>0.0313</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8475</v>
+        <v>0.4546</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.4233</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2754</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1047</v>
+        <v>3.2902</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5065</v>
+        <v>3.9058</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4017</v>
+        <v>-0.6156</v>
       </c>
       <c r="G4" t="n">
         <v>3.3455</v>
@@ -766,13 +766,13 @@
         <v>2.3502</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5461</v>
+        <v>0.7316</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3482</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.198</v>
+        <v>-0.0159</v>
       </c>
       <c r="V4" t="n">
         <v>-2.1578</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6796</v>
+        <v>2.5356</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.8174</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8787</v>
+        <v>1.7183</v>
       </c>
       <c r="G5" t="n">
         <v>1.9607</v>
@@ -844,13 +844,13 @@
         <v>0.5875</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7776</v>
+        <v>0.6337</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1059</v>
+        <v>0.1223</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6718</v>
+        <v>0.5114</v>
       </c>
       <c r="V5" t="n">
         <v>0.3329</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2881</v>
+        <v>2.4547</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4147</v>
+        <v>0.4477</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8734</v>
+        <v>2.0071</v>
       </c>
       <c r="G6" t="n">
         <v>1.9085</v>
@@ -922,13 +922,13 @@
         <v>1.9585</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5996</v>
+        <v>-0.433</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3788</v>
+        <v>0.4117</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9784</v>
+        <v>-0.8447</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5397</v>
+        <v>1.3664</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6881</v>
+        <v>1.3811</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1484</v>
+        <v>-0.0147</v>
       </c>
       <c r="G7" t="n">
         <v>1.8676</v>
@@ -1000,13 +1000,13 @@
         <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>0.065</v>
+        <v>-0.1084</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5987</v>
+        <v>0.2917</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5337</v>
+        <v>-0.4001</v>
       </c>
       <c r="V7" t="n">
         <v>0.3905</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4348</v>
+        <v>-0.1707</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6367</v>
+        <v>-0.3726</v>
       </c>
       <c r="F8" t="n">
         <v>0.2019</v>
@@ -1078,10 +1078,10 @@
         <v>0.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3676</v>
+        <v>-0.1035</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1782</v>
+        <v>0.0859</v>
       </c>
       <c r="U8" t="n">
         <v>-0.1894</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5604</v>
+        <v>-0.709</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0355</v>
+        <v>-1.1574</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4752</v>
+        <v>0.4484</v>
       </c>
       <c r="G9" t="n">
         <v>0.587</v>
@@ -1156,13 +1156,13 @@
         <v>1.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7177</v>
+        <v>0.1337</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6181</v>
+        <v>0.26</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-0.1263</v>
       </c>
       <c r="V9" t="n">
         <v>0.3329</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. GONZALEZ VAZQUEZ</t>
+          <t>M. ROZAS RAMOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1882</v>
+        <v>-1.7486</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3389</v>
+        <v>-2.1059</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8493000000000001</v>
+        <v>0.3573</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.8823</v>
+        <v>-2.069</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.2005</v>
+        <v>-1.1743</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6819</v>
+        <v>-0.8947000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7417</v>
+        <v>-2.0835</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1807</v>
+        <v>-0.7691</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-1.3144</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1406</v>
+        <v>0.0145</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0197</v>
+        <v>-0.4052</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1209</v>
+        <v>0.4197</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9792</v>
+        <v>0.3917</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9792</v>
+        <v>0.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2851</v>
+        <v>0.537</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4029</v>
+        <v>0.3105</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6879999999999999</v>
+        <v>0.2264</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. ROZAS RAMOS</t>
+          <t>S. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3745</v>
+        <v>-1.9195</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8387</v>
+        <v>-1.1771</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4642</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.069</v>
+        <v>-2.8823</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1743</v>
+        <v>-2.2005</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8947000000000001</v>
+        <v>-0.6819</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.0835</v>
+        <v>-1.7417</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7691</v>
+        <v>-1.1807</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3144</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0145</v>
+        <v>-1.1406</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4052</v>
+        <v>-1.0197</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4197</v>
+        <v>-0.1209</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3917</v>
+        <v>0.9792</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3917</v>
+        <v>0.9792</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.0165</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4223</v>
+        <v>0.5646</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3334</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0926</v>
+        <v>-3.5332</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6987</v>
+        <v>-3.2729</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3939</v>
+        <v>-0.2603</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7124</v>
@@ -1390,13 +1390,13 @@
         <v>0.7834</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6349</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5346</v>
+        <v>-0.1088</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1003</v>
+        <v>0.0334</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5495</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.6358</v>
+        <v>20.1208</v>
       </c>
       <c r="E13" t="n">
-        <v>12.9026</v>
+        <v>14.38790000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>5.733299999999999</v>
+        <v>5.733100000000001</v>
       </c>
       <c r="G13" t="n">
         <v>17.8845</v>
@@ -1468,13 +1468,13 @@
         <v>12.73</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6822000000000001</v>
+        <v>2.1673</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8967</v>
+        <v>4.3815</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.2143</v>
+        <v>-2.214400000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-2.8689</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3532</v>
+        <v>2.0917</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9089</v>
+        <v>2.3182</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5557</v>
+        <v>-0.2265</v>
       </c>
       <c r="G14" t="n">
         <v>-0.894</v>
@@ -1546,13 +1546,13 @@
         <v>1.7626</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6169</v>
+        <v>0.1216</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2329</v>
+        <v>0.1764</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.384</v>
+        <v>-0.0548</v>
       </c>
       <c r="V14" t="n">
         <v>1.1014</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>2.135</v>
+        <v>1.828</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.235</v>
+        <v>-0.8819</v>
       </c>
       <c r="G15" t="n">
         <v>0.1618</v>
@@ -1624,13 +1624,13 @@
         <v>0.1958</v>
       </c>
       <c r="S15" t="n">
-        <v>0.267</v>
+        <v>0.313</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6228</v>
+        <v>0.3158</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3559</v>
+        <v>-0.0028</v>
       </c>
       <c r="V15" t="n">
         <v>0.2754</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>B. FRAGA CANTELAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4764</v>
+        <v>0.4071</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2622</v>
+        <v>0.1063</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2143</v>
+        <v>0.3008</v>
       </c>
       <c r="G16" t="n">
-        <v>0.982</v>
+        <v>0.0215</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2085</v>
+        <v>-0.3879</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7734</v>
+        <v>0.4093</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7695</v>
+        <v>0.0204</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1585</v>
+        <v>0.0204</v>
       </c>
       <c r="L16" t="n">
-        <v>0.611</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7875</v>
+        <v>0.001</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9499</v>
+        <v>-0.4083</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1624</v>
+        <v>0.4093</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7834</v>
+        <v>0.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1751</v>
+        <v>0.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6108</v>
+        <v>-0.006</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5087</v>
+        <v>0.0859</v>
       </c>
       <c r="U16" t="n">
-        <v>0.102</v>
+        <v>-0.0919</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.0576</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. FRAGA CANTELAR</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1757</v>
+        <v>0.3372</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0984</v>
+        <v>-0.1472</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2741</v>
+        <v>0.4844</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0215</v>
+        <v>0.982</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3879</v>
+        <v>0.2085</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4093</v>
+        <v>0.7734</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0204</v>
+        <v>1.7695</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0204</v>
+        <v>1.1585</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.611</v>
       </c>
       <c r="M17" t="n">
-        <v>0.001</v>
+        <v>-0.7875</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4083</v>
+        <v>-0.9499</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4093</v>
+        <v>0.1624</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3917</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3917</v>
+        <v>1.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2374</v>
+        <v>0.4715</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1188</v>
+        <v>0.0994</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1186</v>
+        <v>0.3721</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.0576</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1271</v>
+        <v>0.1345</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7116</v>
+        <v>1.6093</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5845</v>
+        <v>-1.4748</v>
       </c>
       <c r="G18" t="n">
         <v>-1.7963</v>
@@ -1858,13 +1858,13 @@
         <v>0.5875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2137</v>
+        <v>-0.2063</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4029</v>
+        <v>0.3005</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6165</v>
+        <v>-0.5068</v>
       </c>
       <c r="V18" t="n">
         <v>1.5495</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6808</v>
+        <v>0.0982</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6113</v>
+        <v>1.7137</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2921</v>
+        <v>-1.6154</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1089</v>
@@ -1936,13 +1936,13 @@
         <v>1.3709</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.944</v>
+        <v>-0.165</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0965</v>
+        <v>0.0059</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8475</v>
+        <v>-0.1708</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9988</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7843</v>
+        <v>-0.961</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5279</v>
+        <v>-1.2209</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2563</v>
+        <v>0.2599</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0768</v>
@@ -2014,13 +2014,13 @@
         <v>0.1958</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9609</v>
+        <v>-0.1376</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.297</v>
+        <v>0.01</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6639</v>
+        <v>-0.1476</v>
       </c>
       <c r="V20" t="n">
         <v>0.0576</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. FUENTES PRADO</t>
+          <t>Y. PINAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2249</v>
+        <v>-1.7284</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7584</v>
+        <v>0.0383</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4664</v>
+        <v>-1.7667</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8155</v>
+        <v>-1.5591</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0476</v>
+        <v>-1.6203</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7679</v>
+        <v>0.0612</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.601</v>
+        <v>0.4606</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0408</v>
+        <v>0.4202</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6418</v>
+        <v>0.0404</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2145</v>
+        <v>-2.0197</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0885</v>
+        <v>-2.0405</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1261</v>
+        <v>0.0208</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5875</v>
+        <v>0.9792</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3917</v>
+        <v>0.9792</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1782</v>
+        <v>-0.5402</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1782</v>
+        <v>-0.4223</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3564</v>
+        <v>-0.1179</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Y. PINAS</t>
+          <t>N. FUENTES PRADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3276</v>
+        <v>-1.8155</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.371</v>
+        <v>-1.3491</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9566</v>
+        <v>-0.4664</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5591</v>
+        <v>-1.8155</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6203</v>
+        <v>-1.0476</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0612</v>
+        <v>-0.7679</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4606</v>
+        <v>-0.601</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4202</v>
+        <v>0.0408</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0404</v>
+        <v>-0.6418</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0197</v>
+        <v>-1.2145</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.0405</v>
+        <v>-1.0885</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0208</v>
+        <v>-0.1261</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9792</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9792</v>
+        <v>0.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1395</v>
+        <v>0.5875</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8316</v>
+        <v>0.2311</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3078</v>
+        <v>0.3564</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0255</v>
+        <v>-4.6589</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8401</v>
+        <v>-2.9658</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1855</v>
+        <v>-1.6931</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8152</v>
@@ -2248,13 +2248,13 @@
         <v>0.5875</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7654</v>
+        <v>0.132</v>
       </c>
       <c r="T23" t="n">
-        <v>1.7256</v>
+        <v>0.5999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9602000000000001</v>
+        <v>-0.4679</v>
       </c>
       <c r="V23" t="n">
         <v>0.3329</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0469</v>
+        <v>-5.3603</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.5419</v>
+        <v>-3.6443</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.505</v>
+        <v>-1.716</v>
       </c>
       <c r="G24" t="n">
         <v>-5.6822</v>
@@ -2326,13 +2326,13 @@
         <v>0.9792</v>
       </c>
       <c r="S24" t="n">
-        <v>1.6145</v>
+        <v>1.3011</v>
       </c>
       <c r="T24" t="n">
-        <v>1.0016</v>
+        <v>0.8993</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6129</v>
+        <v>0.4018</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5782</v>
+        <v>-5.3975</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.2243</v>
+        <v>-4.0197</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3539</v>
+        <v>-1.3778</v>
       </c>
       <c r="G25" t="n">
         <v>-5.3018</v>
@@ -2404,13 +2404,13 @@
         <v>1.1751</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0058</v>
+        <v>0.175</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2923</v>
+        <v>-0.0876</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2865</v>
+        <v>0.2626</v>
       </c>
       <c r="V25" t="n">
         <v>1.492</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.6358</v>
+        <v>-15.9068</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.733000000000001</v>
+        <v>-5.7332</v>
       </c>
       <c r="F26" t="n">
-        <v>-12.9026</v>
+        <v>-10.1735</v>
       </c>
       <c r="G26" t="n">
         <v>-17.8845</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.7861</v>
+        <v>-5.786099999999999</v>
       </c>
       <c r="I26" t="n">
         <v>-12.0987</v>
@@ -2479,16 +2479,16 @@
         <v>-12.7301</v>
       </c>
       <c r="R26" t="n">
-        <v>9.7921</v>
+        <v>9.792100000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6822999999999999</v>
+        <v>2.0466</v>
       </c>
       <c r="T26" t="n">
         <v>2.2143</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.896599999999999</v>
+        <v>-0.1676000000000001</v>
       </c>
       <c r="V26" t="n">
         <v>2.8688</v>
